--- a/data/trans_dic/IP16A10-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,18</t>
+          <t>0,0; 15,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 13,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>0,0; 8,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 11,25</t>
+          <t>2,94; 10,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,01</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,53</t>
+          <t>1,06; 6,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,96</t>
+          <t>1,99; 6,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,23</t>
+          <t>1,06; 4,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,26</t>
+          <t>0,34; 2,9</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 18,49</t>
+          <t>2,26; 19,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,49</t>
+          <t>0,0; 11,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,04</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,92</t>
+          <t>1,06; 9,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,67</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,49</t>
+          <t>2,76; 9,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,07</t>
+          <t>0,6; 4,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,97</t>
+          <t>0,34; 2,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,28</t>
+          <t>0,47; 4,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,6</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,3</t>
+          <t>0,44; 3,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,49</t>
+          <t>2,16; 5,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,44</t>
+          <t>0,97; 3,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,56</t>
+          <t>0,43; 2,56</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3200</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3175</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3479</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2556</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6528</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2375; 8762</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4309</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1305; 8203</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4839</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3350; 11422</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2520; 10045</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>700; 5895</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1661</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>511; 4342</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5276</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3764</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3443</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2912</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>612; 5760</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5577</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4276</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3459; 11637</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1123; 7525</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>558; 4656</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>670; 6984</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1875; 8700</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>659; 5451</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5798; 15658</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3667; 13254</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7953</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A10-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Estudios-trans_dic.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,8</t>
+          <t>0,0; 15,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,86</t>
+          <t>2,86; 10,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,43; 4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,68</t>
+          <t>1,07; 7,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,78</t>
+          <t>1,99; 6,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,21</t>
+          <t>1,02; 4,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,9</t>
+          <t>0,34; 3,22</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 19,25</t>
+          <t>2,26; 20,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,51</t>
+          <t>0,0; 11,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 8,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,96</t>
+          <t>1,07; 9,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,67</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,29</t>
+          <t>2,85; 8,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,02</t>
+          <t>0,64; 3,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,86</t>
+          <t>0,34; 2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,88</t>
+          <t>0,5; 4,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,56</t>
+          <t>0,69; 4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,68</t>
+          <t>0,44; 3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,83</t>
+          <t>2,19; 5,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,51</t>
+          <t>1,01; 3,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,56</t>
+          <t>0,45; 2,53</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3200</t>
+          <t>0; 3233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3175</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>0; 3337</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2556</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2375; 8762</t>
+          <t>2305; 8651</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4592</t>
+          <t>500; 5145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4096</t>
+          <t>0; 3628</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 4857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1305; 8203</t>
+          <t>1313; 8862</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4839</t>
+          <t>0; 4827</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3350; 11422</t>
+          <t>3351; 11614</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2520; 10045</t>
+          <t>2430; 9594</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>700; 5895</t>
+          <t>700; 6560</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>511; 4342</t>
+          <t>510; 4518</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5276</t>
+          <t>0; 5132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3764</t>
+          <t>0; 3290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3443</t>
+          <t>0; 3688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2912</t>
+          <t>0; 3165</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>612; 5760</t>
+          <t>619; 5516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5577</t>
+          <t>0; 5709</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4276</t>
+          <t>0; 3918</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3459; 11637</t>
+          <t>3573; 11072</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1123; 7525</t>
+          <t>1193; 7245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>558; 4656</t>
+          <t>557; 4794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>670; 6984</t>
+          <t>722; 6786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1875; 8700</t>
+          <t>1314; 8057</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>659; 5451</t>
+          <t>656; 5618</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5798; 15658</t>
+          <t>5877; 15209</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3667; 13254</t>
+          <t>3803; 13004</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1349; 7953</t>
+          <t>1393; 7846</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A10-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,29 +678,29 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 16,18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,22</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,96</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,39</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>0,0; 8,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 10,72</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,45</t>
+          <t>1,05; 6,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>3,14; 11,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,22</t>
+          <t>0,43; 4,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,9</t>
+          <t>2,12; 6,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,02</t>
+          <t>1,0; 4,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,22</t>
+          <t>0,34; 3,26</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,46%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 20,03</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,46</t>
+          <t>2,22; 18,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,4</t>
+          <t>0,0; 8,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,54</t>
+          <t>1,07; 9,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,84</t>
+          <t>0,47; 4,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,87</t>
+          <t>0,81; 4,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,95</t>
+          <t>0,45; 3,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,74</t>
+          <t>3,04; 9,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,22</t>
+          <t>0,65; 4,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,79</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,66</t>
+          <t>2,02; 5,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,44</t>
+          <t>1,04; 3,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,53</t>
+          <t>0,45; 2,56</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1306,29 +1306,29 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3277</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2792</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3233</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3059</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3337</t>
+          <t>0; 3598</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3102</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1363,27 +1363,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5136</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1173</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3490</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2305; 8651</t>
+          <t>0; 4836</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>500; 5145</t>
+          <t>1290; 8020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>0; 4305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4857</t>
+          <t>2532; 9081</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1313; 8862</t>
+          <t>493; 4635</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4827</t>
+          <t>0; 4212</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3351; 11614</t>
+          <t>3566; 11718</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2430; 9594</t>
+          <t>2385; 10090</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>700; 6560</t>
+          <t>695; 6632</t>
         </is>
       </c>
     </row>
@@ -1526,27 +1526,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1661</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>589</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>510; 4518</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3290</t>
+          <t>0; 3295</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3688</t>
+          <t>500; 4170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3165</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>619; 5516</t>
+          <t>619; 5734</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5709</t>
+          <t>0; 5112</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3918</t>
+          <t>0; 4007</t>
         </is>
       </c>
     </row>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1762</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3573; 11072</t>
+          <t>677; 6133</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1193; 7245</t>
+          <t>1547; 8784</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>557; 4794</t>
+          <t>661; 4881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>722; 6786</t>
+          <t>3809; 11888</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1314; 8057</t>
+          <t>1211; 7613</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>656; 5618</t>
+          <t>554; 4830</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5877; 15209</t>
+          <t>5434; 14734</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3803; 13004</t>
+          <t>3915; 12980</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1393; 7846</t>
+          <t>1392; 7948</t>
         </is>
       </c>
     </row>
